--- a/Spring 프로젝트 SRS.xlsx
+++ b/Spring 프로젝트 SRS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30219"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{01AB076E-D5E5-4E35-B7D6-04E35DEA9714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{38ADA25F-BB62-41DA-9852-A1B90124D54E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="124">
   <si>
     <t>기능 요구 사항</t>
   </si>
@@ -149,6 +149,18 @@
 등급 산정은 글 작성 혹은 추천 발생 시 컬럼 갱신</t>
   </si>
   <si>
+    <t>M-09</t>
+  </si>
+  <si>
+    <t>마이페이지 - 얼굴 로그인</t>
+  </si>
+  <si>
+    <t>등록한 얼굴로 로그인을 할 수 있음</t>
+  </si>
+  <si>
+    <t>api 가져와서 만들기 x</t>
+  </si>
+  <si>
     <t>게시판 시스템</t>
   </si>
   <si>
@@ -260,13 +272,13 @@
     <t>G-01</t>
   </si>
   <si>
-    <t>캐릭터 정보</t>
-  </si>
-  <si>
-    <t>영웅별 스킬, 상성(카운터 영웅), 팁 조회</t>
-  </si>
-  <si>
-    <t>배틀넷 API를 가져와 활용</t>
+    <t>게임 정보</t>
+  </si>
+  <si>
+    <t>영웅별 스킬, 역할군, 맵(거점) 정보 조회</t>
+  </si>
+  <si>
+    <t>OverFast API 활용</t>
   </si>
   <si>
     <t>G-02</t>
@@ -287,11 +299,7 @@
     <t>모집글 작성</t>
   </si>
   <si>
-    <t>역할군/티어/마이크 사용여부/주 캐릭터 등을 체크박스 선택</t>
-  </si>
-  <si>
-    <t>체크박스 선택 항목들을 조건으로 동적 쿼리
-(MyBatis &lt;if&gt; 또는 JPA Criteria/QueryDSL)를 구성.</t>
+    <t>역할군/티어/마이크 사용여부/주 캐릭터 등을 작성</t>
   </si>
   <si>
     <t>P-02</t>
@@ -415,7 +423,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -448,6 +456,12 @@
       <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="Malgun Gothic"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="10">
@@ -518,7 +532,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -563,6 +577,10 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -878,7 +896,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr defaultRowHeight="31.5"/>
   <cols>
     <col min="1" max="1" width="10.375" style="2" bestFit="1" customWidth="1"/>
@@ -1048,64 +1066,67 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="9" t="s">
+    <row r="13" spans="1:5" ht="96.75" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
+      <c r="B13" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="B14" s="17"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="61.5">
-      <c r="A17" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="213.75">
+    <row r="18" spans="1:5" ht="61.5">
       <c r="A18" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="2" t="s">
         <v>42</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+    </row>
+    <row r="19" spans="1:5" ht="213.75">
       <c r="A19" s="2" t="s">
         <v>44</v>
       </c>
@@ -1118,93 +1139,93 @@
       <c r="D19" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="122.25">
+      <c r="E19" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="3" t="s">
         <v>49</v>
       </c>
+      <c r="C20" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="D20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="122.25">
       <c r="A21" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="10" t="s">
+      <c r="E21" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A25" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1214,72 +1235,72 @@
       <c r="B28" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E28" s="4"/>
-    </row>
-    <row r="29" spans="1:5" ht="92.25">
+      <c r="E28" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C29" s="2" t="s">
         <v>67</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="11" t="s">
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="1:5" ht="92.25">
+      <c r="A30" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
+      <c r="B30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A33" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>73</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1296,50 +1317,50 @@
         <v>28</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B40" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C40" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E40" s="2" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="122.25">
-      <c r="A40" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1355,6 +1376,7 @@
       <c r="D41" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="E41" s="3"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2" t="s">
@@ -1370,44 +1392,44 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="13" t="s">
+    <row r="43" spans="1:5">
+      <c r="A43" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
+      <c r="B43" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A46" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" s="13"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2" t="s">
-        <v>89</v>
+        <v>2</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>90</v>
+        <v>3</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>28</v>
+        <v>5</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1424,44 +1446,44 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="8" t="s">
+    <row r="49" spans="1:5">
+      <c r="A49" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
+      <c r="B49" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A52" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2" t="s">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>97</v>
+        <v>3</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>18</v>
+        <v>5</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1471,7 +1493,7 @@
       <c r="B54" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="2" t="s">
         <v>101</v>
       </c>
       <c r="D54" s="2" t="s">
@@ -1485,7 +1507,7 @@
       <c r="B55" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="4" t="s">
         <v>104</v>
       </c>
       <c r="D55" s="2" t="s">
@@ -1503,6 +1525,20 @@
         <v>107</v>
       </c>
       <c r="D56" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1511,12 +1547,12 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A46:E46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1533,7 +1569,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="23.25">
       <c r="A1" s="16" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -1542,10 +1578,10 @@
     </row>
     <row r="2" spans="1:5" s="1" customFormat="1" ht="20.25">
       <c r="A2" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C2" s="15"/>
       <c r="D2" s="15"/>
@@ -1553,10 +1589,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C3" s="14"/>
       <c r="D3" s="14"/>
@@ -1564,10 +1600,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
@@ -1575,10 +1611,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -1586,10 +1622,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -1597,10 +1633,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
